--- a/my_demo_project.xlsx
+++ b/my_demo_project.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Adnan Khan\Documents\GitHub\Demo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AE90ED8-FB82-413E-9D0A-02ECAE8646E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A1C7004-DC47-40C8-809D-522B6F178130}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -493,6 +493,9 @@
       <c r="C14">
         <v>-10</v>
       </c>
+      <c r="F14">
+        <v>9</v>
+      </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15">

--- a/my_demo_project.xlsx
+++ b/my_demo_project.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Adnan Khan\Documents\GitHub\Demo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adnan\Documents\GitHub\Demo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A1C7004-DC47-40C8-809D-522B6F178130}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +35,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -354,11 +353,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1">
         <v>1</v>
       </c>
@@ -366,7 +365,7 @@
         <v>-8</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>2</v>
       </c>
@@ -374,7 +373,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>3</v>
       </c>
@@ -382,7 +381,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>4</v>
       </c>
@@ -390,7 +389,7 @@
         <v>-9</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>5</v>
       </c>
@@ -398,7 +397,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>6</v>
       </c>
@@ -409,7 +408,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>7</v>
       </c>
@@ -420,7 +419,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>8</v>
       </c>
@@ -431,7 +430,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>9</v>
       </c>
@@ -442,7 +441,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>10</v>
       </c>
@@ -453,7 +452,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>11</v>
       </c>
@@ -464,7 +463,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>12</v>
       </c>
@@ -475,7 +474,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>13</v>
       </c>
@@ -486,7 +485,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>14</v>
       </c>
@@ -497,15 +496,18 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>15</v>
       </c>
       <c r="C15">
         <v>-9</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>16</v>
       </c>
@@ -513,7 +515,7 @@
         <v>-3</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>17</v>
       </c>
@@ -521,7 +523,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>18</v>
       </c>
@@ -529,7 +531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>19</v>
       </c>
@@ -537,7 +539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>20</v>
       </c>

--- a/my_demo_project.xlsx
+++ b/my_demo_project.xlsx
@@ -514,6 +514,9 @@
       <c r="C16">
         <v>-3</v>
       </c>
+      <c r="F16">
+        <v>11</v>
+      </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17">

--- a/my_demo_project.xlsx
+++ b/my_demo_project.xlsx
@@ -518,15 +518,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>17</v>
       </c>
       <c r="C17">
         <v>-2</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="F17">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>18</v>
       </c>
@@ -534,7 +537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>19</v>
       </c>
@@ -542,7 +545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>20</v>
       </c>
